--- a/docs/需求讨论-20260814.xlsx
+++ b/docs/需求讨论-20260814.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>需求</t>
   </si>
@@ -84,13 +84,25 @@
 优化成二级菜单，不要在单页面存现多个功能点，最好最好一个管理一个页面。</t>
   </si>
   <si>
-    <t>8. 推广分成：教练分成：单独配置用户推广信息（折扣、成家返点）</t>
-  </si>
-  <si>
-    <t>在综合运营平台中，需要有一个推广管理、推广配置模版，可以配置教练分成、和每个商家分成比例配置。推广角色类型：会员（可以配置全部会员、单独一个会员等），可以配置商家推广相关配置。和相关折扣。    整个平台需要有推广规则。那个会员推广了那个会员，都有独立的推广二维码和推广链接。然后会员就挂靠在此推广链接下.  然后记录每个会员消费金额，对应根据返点规则，计算出应该应该返回多少钱。管理员会通过线下返钱，同时并同步到线上记录状态，当前金额已返现等相关状态。请按照业界具体流程进行设计和完成，流程更加专业。每个会员应该有独立的推广二维码，同时可以配置返点数值。也可以配置进行推广后的关联的会员，享受的折扣，需要进行配置。同时也要在基础配置总增加一项推广配置，可以配置相关推广相关的配置。</t>
+    <t>8. 完成统一推广方案 和 健身业务系统中的教练分成方案，
+（1）、在综合运营平台中可以配置会员推广信息（下级会员消费折扣和 下级会员消费商家返点比例）
+（2）、完成健身业务系统中的教练提成业务流程。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、每个会员有一个推广二维码及推广链接。
+2、根据推广二维码进来的会员为当前二维码下级会员，只进行一级关联
+3、下级会员所有的消费金额会进行返点金额到对应上级的推广二维码对应的会员返点余额中。
+4、可以配置每个会员对应的推广二维码当前返点比例
+5、可以配置每个会员对应的推广二维码下级会员享受消费折扣
+6、在健身业务系统中，需要配置每个教练对应的私教课佣金比例。
+7、健身教练登陆账号后可以查看对应的佣金信息及提现数据，提现是线下操作，同步至线上当前平台状态。
+</t>
   </si>
   <si>
     <t>9. 独立创建：健身房小程序</t>
+  </si>
+  <si>
+    <t>目前还是集成在一起</t>
   </si>
   <si>
     <t>10. 平台8月底可用</t>
@@ -1423,15 +1435,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="286" spans="1:4">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="269" spans="1:4">
+      <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
+      <c r="C9" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -1441,8 +1453,10 @@
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1451,10 +1465,10 @@
     </row>
     <row r="11" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1463,11 +1477,11 @@
     </row>
     <row r="12" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
+      <c r="C12" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -1475,7 +1489,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
@@ -1487,17 +1501,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/需求讨论-20260814.xlsx
+++ b/docs/需求讨论-20260814.xlsx
@@ -47,9 +47,6 @@
     <t>已完成</t>
   </si>
   <si>
-    <t>未完成</t>
-  </si>
-  <si>
     <t>2. 超管-修改密码</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
   </si>
   <si>
     <t>10. 平台8月底可用</t>
+  </si>
+  <si>
+    <t>未完成</t>
   </si>
   <si>
     <t>11. 增加数据导出</t>
@@ -1349,130 +1349,130 @@
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>6</v>
+      <c r="D3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>6</v>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="51" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>6</v>
+      <c r="D5" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>6</v>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="68" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>6</v>
+      <c r="D7" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="68" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>6</v>
+      <c r="D8" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="269" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>6</v>
+      <c r="D9" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>6</v>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
@@ -1483,8 +1483,8 @@
       <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>6</v>
+      <c r="D12" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -1495,8 +1495,8 @@
       <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>6</v>
+      <c r="D13" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -1507,8 +1507,8 @@
       <c r="C14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>6</v>
+      <c r="D14" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
